--- a/erp-server/erp-server-fms/src/main/resources/excel/assetDisposalTemplate.xlsx
+++ b/erp-server/erp-server-fms/src/main/resources/excel/assetDisposalTemplate.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="22560" windowHeight="11120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,27 +27,119 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>序号</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>序号</t>
+    </r>
   </si>
   <si>
-    <t>业务日期</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>业务日期</t>
+    </r>
   </si>
   <si>
-    <t>单据状态</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>资产组织</t>
+    </r>
   </si>
   <si>
-    <t>处置方式</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>处置方式</t>
+    </r>
   </si>
   <si>
-    <t>资产组织</t>
+    <t>处置原因</t>
   </si>
   <si>
-    <t>卡片编码</t>
-  </si>
-  <si>
-    <t>资产名称</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>卡片编码</t>
+    </r>
   </si>
   <si>
     <t>处置币别</t>
@@ -61,22 +151,54 @@
     <t>残值收入（含税）</t>
   </si>
   <si>
-    <t>数量</t>
+    <t>发票类型</t>
   </si>
   <si>
-    <t>处置数量</t>
+    <t>税率</t>
   </si>
   <si>
-    <t>审核人（最新）</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>资产编码</t>
+    </r>
   </si>
   <si>
-    <t>审核完成时间</t>
-  </si>
-  <si>
-    <t>创建人</t>
-  </si>
-  <si>
-    <t>创建时间</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC00000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>数量</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -89,7 +211,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -98,16 +220,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
+      <sz val="10.5"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -559,163 +690,163 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -769,7 +900,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1028,102 +1373,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="D1:S1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="3" width="23.75" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="15.75" customWidth="1"/>
-    <col min="6" max="7" width="10.125" customWidth="1"/>
-    <col min="8" max="8" width="8.625" customWidth="1"/>
-    <col min="9" max="11" width="16.125" customWidth="1"/>
-    <col min="12" max="12" width="17.125" customWidth="1"/>
-    <col min="13" max="13" width="20.375" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="14.875" customWidth="1"/>
-    <col min="17" max="17" width="12.25" customWidth="1"/>
+    <col min="1" max="1" width="9.81818181818182" customWidth="1"/>
+    <col min="2" max="2" width="15.9090909090909" customWidth="1"/>
+    <col min="3" max="3" width="16.1818181818182" customWidth="1"/>
+    <col min="4" max="4" width="12.0909090909091" customWidth="1"/>
+    <col min="5" max="5" width="12.9090909090909" customWidth="1"/>
+    <col min="6" max="6" width="17.0909090909091" customWidth="1"/>
+    <col min="7" max="7" width="11.9090909090909" customWidth="1"/>
+    <col min="8" max="8" width="10.2727272727273" customWidth="1"/>
+    <col min="9" max="9" width="18.2727272727273" customWidth="1"/>
+    <col min="10" max="10" width="16.3636363636364" customWidth="1"/>
+    <col min="12" max="12" width="12.8181818181818" customWidth="1"/>
+    <col min="13" max="13" width="12.3636363636364" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:19">
-      <c r="D1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" ht="13.5" spans="1:13">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+      <formula1>"报废"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
+      <formula1>"普通发票,增值税发票"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-fms/src/main/resources/excel/assetDisposalTemplate.xlsx
+++ b/erp-server/erp-server-fms/src/main/resources/excel/assetDisposalTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22560" windowHeight="11120"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,13 +52,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -96,13 +89,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFC00000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -121,13 +107,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFC00000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -154,17 +133,10 @@
     <t>发票类型</t>
   </si>
   <si>
-    <t>税率</t>
+    <t>税率(%)</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFC00000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -180,13 +152,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FFC00000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1373,24 +1338,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="9.81818181818182" customWidth="1"/>
-    <col min="2" max="2" width="15.9090909090909" customWidth="1"/>
-    <col min="3" max="3" width="16.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="12.0909090909091" customWidth="1"/>
-    <col min="5" max="5" width="12.9090909090909" customWidth="1"/>
-    <col min="6" max="6" width="17.0909090909091" customWidth="1"/>
-    <col min="7" max="7" width="11.9090909090909" customWidth="1"/>
-    <col min="8" max="8" width="10.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="18.2727272727273" customWidth="1"/>
-    <col min="10" max="10" width="16.3636363636364" customWidth="1"/>
-    <col min="12" max="12" width="12.8181818181818" customWidth="1"/>
-    <col min="13" max="13" width="12.3636363636364" customWidth="1"/>
+    <col min="1" max="1" width="9.81666666666667" customWidth="1"/>
+    <col min="2" max="2" width="15.9083333333333" customWidth="1"/>
+    <col min="3" max="3" width="16.1833333333333" customWidth="1"/>
+    <col min="4" max="4" width="12.0916666666667" customWidth="1"/>
+    <col min="5" max="5" width="12.9083333333333" customWidth="1"/>
+    <col min="6" max="6" width="17.0916666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.9083333333333" customWidth="1"/>
+    <col min="8" max="8" width="10.275" customWidth="1"/>
+    <col min="9" max="9" width="18.275" customWidth="1"/>
+    <col min="10" max="10" width="16.3666666666667" customWidth="1"/>
+    <col min="12" max="12" width="12.8166666666667" customWidth="1"/>
+    <col min="13" max="13" width="12.3666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="13.5" spans="1:13">
+    <row r="1" s="1" customFormat="1" ht="12.75" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1431,6 +1396,7 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" ht="12" customHeight="1"/>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
